--- a/examples/outputs/Birgo RR Exhibits - Eagles Eyriev09.10.26.xlsx
+++ b/examples/outputs/Birgo RR Exhibits - Eagles Eyriev09.10.26.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Unit Mix based on # of Beds" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Pres. Rent Roll" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="OneLineRR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Source" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="15">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="#0\ &quot;Units&quot;"/>
     <numFmt numFmtId="165" formatCode="#\ &quot;Units&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0\ &quot;SF&quot;"/>
@@ -36,6 +37,10 @@
     <numFmt numFmtId="176" formatCode="mm\/dd\/yyyy"/>
     <numFmt numFmtId="177" formatCode="0.0"/>
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="#,##0.00;[Red]#,##0.00"/>
+    <numFmt numFmtId="180" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="181" formatCode="#,##0.00;(#,##0.00)"/>
+    <numFmt numFmtId="182" formatCode="#,##0;[Red]#,##0"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -153,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -387,6 +392,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -14541,4 +14552,4836 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:AK112"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13.57142857142857" customWidth="1" min="1" max="1"/>
+    <col width="10.71428571428571" customWidth="1" min="4" max="4"/>
+    <col width="13.57142857142857" customWidth="1" min="5" max="5"/>
+    <col width="10.71428571428571" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="26" max="26"/>
+    <col width="9" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="9" customWidth="1" min="32" max="32"/>
+    <col width="9" customWidth="1" min="33" max="33"/>
+    <col width="9" customWidth="1" min="34" max="34"/>
+    <col width="9" customWidth="1" min="35" max="35"/>
+    <col width="9" customWidth="1" min="36" max="36"/>
+    <col width="9" customWidth="1" min="37" max="37"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Rent Roll</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Eagles Eyrie</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Unit Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Property Look-Up Code</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bldg-Unit</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Unit Type</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SQFT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Unit Status</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Resident</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Move-In</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Lease Start</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Lease End</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Market Rent (RI)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Scheduled Charges</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Deposit Held</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2421 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D8" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Price, Ally</t>
+        </is>
+      </c>
+      <c r="G8" s="88" t="n">
+        <v>46164</v>
+      </c>
+      <c r="H8" s="88" t="n">
+        <v>46164</v>
+      </c>
+      <c r="I8" s="88" t="n">
+        <v>46530</v>
+      </c>
+      <c r="J8" s="89" t="n">
+        <v>1394</v>
+      </c>
+      <c r="K8" s="89" t="n">
+        <v>1367</v>
+      </c>
+      <c r="L8" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2423 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D9" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Winn, Sterling</t>
+        </is>
+      </c>
+      <c r="G9" s="88" t="n">
+        <v>45355</v>
+      </c>
+      <c r="H9" s="88" t="n">
+        <v>46118</v>
+      </c>
+      <c r="I9" s="88" t="n">
+        <v>46488</v>
+      </c>
+      <c r="J9" s="89" t="n">
+        <v>1584</v>
+      </c>
+      <c r="K9" s="89" t="n">
+        <v>1525</v>
+      </c>
+      <c r="L9" s="89" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2425 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D10" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>harris, shonna</t>
+        </is>
+      </c>
+      <c r="G10" s="88" t="n">
+        <v>45930</v>
+      </c>
+      <c r="H10" s="88" t="n">
+        <v>45930</v>
+      </c>
+      <c r="I10" s="88" t="n">
+        <v>46481</v>
+      </c>
+      <c r="J10" s="89" t="n">
+        <v>1394</v>
+      </c>
+      <c r="K10" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="L10" s="89" t="n">
+        <v>687.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2425 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D11" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Adams, David</t>
+        </is>
+      </c>
+      <c r="G11" s="88" t="n">
+        <v>46269</v>
+      </c>
+      <c r="H11" s="88" t="n">
+        <v>46269</v>
+      </c>
+      <c r="I11" s="88" t="n">
+        <v>46635</v>
+      </c>
+      <c r="J11" s="89" t="n">
+        <v>1394</v>
+      </c>
+      <c r="K11" s="89" t="n">
+        <v>1304</v>
+      </c>
+      <c r="L11" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2426 Eagles Eyrie-1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D12" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stelly, Joshua</t>
+        </is>
+      </c>
+      <c r="G12" s="88" t="n">
+        <v>44974</v>
+      </c>
+      <c r="H12" s="88" t="n">
+        <v>46181</v>
+      </c>
+      <c r="I12" s="88" t="n">
+        <v>46551</v>
+      </c>
+      <c r="J12" s="89" t="n">
+        <v>1205</v>
+      </c>
+      <c r="K12" s="89" t="n">
+        <v>1123</v>
+      </c>
+      <c r="L12" s="89" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2426 Eagles Eyrie-2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D13" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dennis, Dymond</t>
+        </is>
+      </c>
+      <c r="G13" s="88" t="n">
+        <v>46218</v>
+      </c>
+      <c r="H13" s="88" t="n">
+        <v>46218</v>
+      </c>
+      <c r="I13" s="88" t="n">
+        <v>46586</v>
+      </c>
+      <c r="J13" s="89" t="n">
+        <v>1280</v>
+      </c>
+      <c r="K13" s="89" t="n">
+        <v>1292</v>
+      </c>
+      <c r="L13" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2427 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D14" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Maynor, Franklin</t>
+        </is>
+      </c>
+      <c r="G14" s="88" t="n">
+        <v>42266</v>
+      </c>
+      <c r="H14" s="88" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I14" s="88" t="n">
+        <v>46299</v>
+      </c>
+      <c r="J14" s="89" t="n">
+        <v>1584</v>
+      </c>
+      <c r="K14" s="89" t="n">
+        <v>1405</v>
+      </c>
+      <c r="L14" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2427 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D15" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rowan, Kaleb</t>
+        </is>
+      </c>
+      <c r="G15" s="88" t="n">
+        <v>46241</v>
+      </c>
+      <c r="H15" s="88" t="n">
+        <v>46241</v>
+      </c>
+      <c r="I15" s="88" t="n">
+        <v>46607</v>
+      </c>
+      <c r="J15" s="89" t="n">
+        <v>1784</v>
+      </c>
+      <c r="K15" s="89" t="n">
+        <v>1776</v>
+      </c>
+      <c r="L15" s="89" t="n">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2428 Eagles Eyrie-3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D16" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Hagerman, Maureen</t>
+        </is>
+      </c>
+      <c r="G16" s="88" t="n">
+        <v>42686</v>
+      </c>
+      <c r="H16" s="88" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I16" s="88" t="n">
+        <v>46418</v>
+      </c>
+      <c r="J16" s="89" t="n">
+        <v>1205</v>
+      </c>
+      <c r="K16" s="89" t="n">
+        <v>1140</v>
+      </c>
+      <c r="L16" s="89" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2428 Eagles Eyrie-4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D17" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Hart, Patricia</t>
+        </is>
+      </c>
+      <c r="G17" s="88" t="n">
+        <v>44151</v>
+      </c>
+      <c r="H17" s="88" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I17" s="88" t="n">
+        <v>46418</v>
+      </c>
+      <c r="J17" s="89" t="n">
+        <v>1205</v>
+      </c>
+      <c r="K17" s="89" t="n">
+        <v>1139</v>
+      </c>
+      <c r="L17" s="89" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2428 Eagles Eyrie-5</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D18" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Cole, Latasha</t>
+        </is>
+      </c>
+      <c r="G18" s="88" t="n">
+        <v>44420</v>
+      </c>
+      <c r="H18" s="88" t="n">
+        <v>46209</v>
+      </c>
+      <c r="I18" s="88" t="n">
+        <v>46579</v>
+      </c>
+      <c r="J18" s="89" t="n">
+        <v>1255</v>
+      </c>
+      <c r="K18" s="89" t="n">
+        <v>1276</v>
+      </c>
+      <c r="L18" s="89" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2428 Eagles Eyrie-6</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D19" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Brown, Termell</t>
+        </is>
+      </c>
+      <c r="G19" s="88" t="n">
+        <v>46148</v>
+      </c>
+      <c r="H19" s="88" t="n">
+        <v>46148</v>
+      </c>
+      <c r="I19" s="88" t="n">
+        <v>46488</v>
+      </c>
+      <c r="J19" s="89" t="n">
+        <v>1280</v>
+      </c>
+      <c r="K19" s="89" t="n">
+        <v>1214</v>
+      </c>
+      <c r="L19" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2429 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D20" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>haney, rose</t>
+        </is>
+      </c>
+      <c r="G20" s="88" t="n">
+        <v>46251</v>
+      </c>
+      <c r="H20" s="88" t="n">
+        <v>46251</v>
+      </c>
+      <c r="I20" s="88" t="n">
+        <v>46621</v>
+      </c>
+      <c r="J20" s="89" t="n">
+        <v>1394</v>
+      </c>
+      <c r="K20" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="L20" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2429 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D21" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Outland, Bradley</t>
+        </is>
+      </c>
+      <c r="G21" s="88" t="n">
+        <v>45429</v>
+      </c>
+      <c r="H21" s="88" t="n">
+        <v>46174</v>
+      </c>
+      <c r="I21" s="88" t="n">
+        <v>46544</v>
+      </c>
+      <c r="J21" s="89" t="n">
+        <v>1319</v>
+      </c>
+      <c r="K21" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L21" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2430 Eagles Eyrie-1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D22" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Capossela, David</t>
+        </is>
+      </c>
+      <c r="G22" s="88" t="n">
+        <v>44407</v>
+      </c>
+      <c r="H22" s="88" t="n">
+        <v>46209</v>
+      </c>
+      <c r="I22" s="88" t="n">
+        <v>46579</v>
+      </c>
+      <c r="J22" s="89" t="n">
+        <v>1205</v>
+      </c>
+      <c r="K22" s="89" t="n">
+        <v>1126</v>
+      </c>
+      <c r="L22" s="89" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2430 Eagles Eyrie-2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D23" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Cash, Alexis</t>
+        </is>
+      </c>
+      <c r="G23" s="88" t="n">
+        <v>45170</v>
+      </c>
+      <c r="H23" s="88" t="n">
+        <v>46209</v>
+      </c>
+      <c r="I23" s="88" t="n">
+        <v>46579</v>
+      </c>
+      <c r="J23" s="89" t="n">
+        <v>1205</v>
+      </c>
+      <c r="K23" s="89" t="n">
+        <v>1180</v>
+      </c>
+      <c r="L23" s="89" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2431 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D24" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Notice Unrented</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Smith, Tyrone</t>
+        </is>
+      </c>
+      <c r="G24" s="88" t="n">
+        <v>44393</v>
+      </c>
+      <c r="H24" s="88" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I24" s="88" t="n">
+        <v>46299</v>
+      </c>
+      <c r="J24" s="89" t="n">
+        <v>1525</v>
+      </c>
+      <c r="K24" s="89" t="n">
+        <v>1465</v>
+      </c>
+      <c r="L24" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2431 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D25" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vance, James</t>
+        </is>
+      </c>
+      <c r="G25" s="88" t="n">
+        <v>45177</v>
+      </c>
+      <c r="H25" s="88" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I25" s="88" t="n">
+        <v>46299</v>
+      </c>
+      <c r="J25" s="89" t="n">
+        <v>1584</v>
+      </c>
+      <c r="K25" s="89" t="n">
+        <v>1405</v>
+      </c>
+      <c r="L25" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2432 Eagles Eyrie-3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D26" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Vacant Rented Ready</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="J26" s="89" t="n">
+        <v>1330</v>
+      </c>
+      <c r="K26" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2432 Eagles Eyrie-4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D27" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fenner, Chris</t>
+        </is>
+      </c>
+      <c r="G27" s="88" t="n">
+        <v>45702</v>
+      </c>
+      <c r="H27" s="88" t="n">
+        <v>46160</v>
+      </c>
+      <c r="I27" s="88" t="n">
+        <v>46530</v>
+      </c>
+      <c r="J27" s="89" t="n">
+        <v>1255</v>
+      </c>
+      <c r="K27" s="89" t="n">
+        <v>1180</v>
+      </c>
+      <c r="L27" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2432 Eagles Eyrie-5</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D28" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Davis, Junion</t>
+        </is>
+      </c>
+      <c r="G28" s="88" t="n">
+        <v>45772</v>
+      </c>
+      <c r="H28" s="88" t="n">
+        <v>46146</v>
+      </c>
+      <c r="I28" s="88" t="n">
+        <v>46516</v>
+      </c>
+      <c r="J28" s="89" t="n">
+        <v>1205</v>
+      </c>
+      <c r="K28" s="89" t="n">
+        <v>1154</v>
+      </c>
+      <c r="L28" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2432 Eagles Eyrie-6</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D29" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Notice Unrented</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bohn, Noah</t>
+        </is>
+      </c>
+      <c r="G29" s="88" t="n">
+        <v>45915</v>
+      </c>
+      <c r="H29" s="88" t="n">
+        <v>45915</v>
+      </c>
+      <c r="I29" s="88" t="n">
+        <v>46285</v>
+      </c>
+      <c r="J29" s="89" t="n">
+        <v>1330</v>
+      </c>
+      <c r="K29" s="89" t="n">
+        <v>1309</v>
+      </c>
+      <c r="L29" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2433 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D30" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ghramm, Malia</t>
+        </is>
+      </c>
+      <c r="G30" s="88" t="n">
+        <v>45992</v>
+      </c>
+      <c r="H30" s="88" t="n">
+        <v>45992</v>
+      </c>
+      <c r="I30" s="88" t="n">
+        <v>46299</v>
+      </c>
+      <c r="J30" s="89" t="n">
+        <v>1394</v>
+      </c>
+      <c r="K30" s="89" t="n">
+        <v>1385</v>
+      </c>
+      <c r="L30" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2433 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D31" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tarbis, Evan</t>
+        </is>
+      </c>
+      <c r="G31" s="88" t="n">
+        <v>44927</v>
+      </c>
+      <c r="H31" s="88" t="n">
+        <v>46118</v>
+      </c>
+      <c r="I31" s="88" t="n">
+        <v>46488</v>
+      </c>
+      <c r="J31" s="89" t="n">
+        <v>1319</v>
+      </c>
+      <c r="K31" s="89" t="n">
+        <v>1278</v>
+      </c>
+      <c r="L31" s="89" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2434 Eagles Eyrie-1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D32" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Wilbers, Seth</t>
+        </is>
+      </c>
+      <c r="G32" s="88" t="n">
+        <v>46130</v>
+      </c>
+      <c r="H32" s="88" t="n">
+        <v>46130</v>
+      </c>
+      <c r="I32" s="88" t="n">
+        <v>46467</v>
+      </c>
+      <c r="J32" s="89" t="n">
+        <v>1280</v>
+      </c>
+      <c r="K32" s="89" t="n">
+        <v>1253</v>
+      </c>
+      <c r="L32" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2434 Eagles Eyrie-2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D33" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Zinious, John</t>
+        </is>
+      </c>
+      <c r="G33" s="88" t="n">
+        <v>44435</v>
+      </c>
+      <c r="H33" s="88" t="n">
+        <v>46209</v>
+      </c>
+      <c r="I33" s="88" t="n">
+        <v>46579</v>
+      </c>
+      <c r="J33" s="89" t="n">
+        <v>1205</v>
+      </c>
+      <c r="K33" s="89" t="n">
+        <v>1159</v>
+      </c>
+      <c r="L33" s="89" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2435 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D34" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>McCray, William</t>
+        </is>
+      </c>
+      <c r="G34" s="88" t="n">
+        <v>45268</v>
+      </c>
+      <c r="H34" s="88" t="n">
+        <v>46118</v>
+      </c>
+      <c r="I34" s="88" t="n">
+        <v>46488</v>
+      </c>
+      <c r="J34" s="89" t="n">
+        <v>1584</v>
+      </c>
+      <c r="K34" s="89" t="n">
+        <v>1310</v>
+      </c>
+      <c r="L34" s="89" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2435 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D35" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dailey, Emma</t>
+        </is>
+      </c>
+      <c r="G35" s="88" t="n">
+        <v>41365</v>
+      </c>
+      <c r="H35" s="88" t="n">
+        <v>46118</v>
+      </c>
+      <c r="I35" s="88" t="n">
+        <v>46488</v>
+      </c>
+      <c r="J35" s="89" t="n">
+        <v>1584</v>
+      </c>
+      <c r="K35" s="89" t="n">
+        <v>1488</v>
+      </c>
+      <c r="L35" s="89" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2436 Eagles Eyrie-3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D36" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>MeNefee, Marian</t>
+        </is>
+      </c>
+      <c r="G36" s="88" t="n">
+        <v>42552</v>
+      </c>
+      <c r="H36" s="88" t="n">
+        <v>46209</v>
+      </c>
+      <c r="I36" s="88" t="n">
+        <v>46579</v>
+      </c>
+      <c r="J36" s="89" t="n">
+        <v>1205</v>
+      </c>
+      <c r="K36" s="89" t="n">
+        <v>1159</v>
+      </c>
+      <c r="L36" s="89" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2436 Eagles Eyrie-4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D37" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Exum, Connor</t>
+        </is>
+      </c>
+      <c r="G37" s="88" t="n">
+        <v>45751</v>
+      </c>
+      <c r="H37" s="88" t="n">
+        <v>46153</v>
+      </c>
+      <c r="I37" s="88" t="n">
+        <v>46523</v>
+      </c>
+      <c r="J37" s="89" t="n">
+        <v>1205</v>
+      </c>
+      <c r="K37" s="89" t="n">
+        <v>1173</v>
+      </c>
+      <c r="L37" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2436 Eagles Eyrie-5</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D38" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Quispe Mendoza, Elvira</t>
+        </is>
+      </c>
+      <c r="G38" s="88" t="n">
+        <v>46164</v>
+      </c>
+      <c r="H38" s="88" t="n">
+        <v>46164</v>
+      </c>
+      <c r="I38" s="88" t="n">
+        <v>46467</v>
+      </c>
+      <c r="J38" s="89" t="n">
+        <v>1280</v>
+      </c>
+      <c r="K38" s="89" t="n">
+        <v>1252</v>
+      </c>
+      <c r="L38" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2436 Eagles Eyrie-6</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D39" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Hetherington, Emma</t>
+        </is>
+      </c>
+      <c r="G39" s="88" t="n">
+        <v>44957</v>
+      </c>
+      <c r="H39" s="88" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I39" s="88" t="n">
+        <v>46635</v>
+      </c>
+      <c r="J39" s="89" t="n">
+        <v>1205</v>
+      </c>
+      <c r="K39" s="89" t="n">
+        <v>1174</v>
+      </c>
+      <c r="L39" s="89" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2437 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D40" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Busam, Byron</t>
+        </is>
+      </c>
+      <c r="G40" s="88" t="n">
+        <v>44958</v>
+      </c>
+      <c r="H40" s="88" t="n">
+        <v>46146</v>
+      </c>
+      <c r="I40" s="88" t="n">
+        <v>46516</v>
+      </c>
+      <c r="J40" s="89" t="n">
+        <v>1319</v>
+      </c>
+      <c r="K40" s="89" t="n">
+        <v>1229</v>
+      </c>
+      <c r="L40" s="89" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2437 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D41" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blincoe, Ray</t>
+        </is>
+      </c>
+      <c r="G41" s="88" t="n">
+        <v>45481</v>
+      </c>
+      <c r="H41" s="88" t="n">
+        <v>46209</v>
+      </c>
+      <c r="I41" s="88" t="n">
+        <v>46579</v>
+      </c>
+      <c r="J41" s="89" t="n">
+        <v>1319</v>
+      </c>
+      <c r="K41" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L41" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2438 Eagles Eyrie-1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D42" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Wakeland, Sally</t>
+        </is>
+      </c>
+      <c r="G42" s="88" t="n">
+        <v>46043</v>
+      </c>
+      <c r="H42" s="88" t="n">
+        <v>46043</v>
+      </c>
+      <c r="I42" s="88" t="n">
+        <v>46411</v>
+      </c>
+      <c r="J42" s="89" t="n">
+        <v>1330</v>
+      </c>
+      <c r="K42" s="89" t="n">
+        <v>1394</v>
+      </c>
+      <c r="L42" s="89" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2438 Eagles Eyrie-2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D43" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gallini, Andrew</t>
+        </is>
+      </c>
+      <c r="G43" s="88" t="n">
+        <v>46044</v>
+      </c>
+      <c r="H43" s="88" t="n">
+        <v>46044</v>
+      </c>
+      <c r="I43" s="88" t="n">
+        <v>46411</v>
+      </c>
+      <c r="J43" s="89" t="n">
+        <v>1405</v>
+      </c>
+      <c r="K43" s="89" t="n">
+        <v>1245</v>
+      </c>
+      <c r="L43" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2439 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D44" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knox, Donte</t>
+        </is>
+      </c>
+      <c r="G44" s="88" t="n">
+        <v>46031</v>
+      </c>
+      <c r="H44" s="88" t="n">
+        <v>46031</v>
+      </c>
+      <c r="I44" s="88" t="n">
+        <v>46579</v>
+      </c>
+      <c r="J44" s="89" t="n">
+        <v>1709</v>
+      </c>
+      <c r="K44" s="89" t="n">
+        <v>1614</v>
+      </c>
+      <c r="L44" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2439 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D45" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Poignard-Schaffer, Bernita</t>
+        </is>
+      </c>
+      <c r="G45" s="88" t="n">
+        <v>45401</v>
+      </c>
+      <c r="H45" s="88" t="n">
+        <v>46146</v>
+      </c>
+      <c r="I45" s="88" t="n">
+        <v>46516</v>
+      </c>
+      <c r="J45" s="89" t="n">
+        <v>1584</v>
+      </c>
+      <c r="K45" s="89" t="n">
+        <v>1465</v>
+      </c>
+      <c r="L45" s="89" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2440 Eagles Eyrie-3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D46" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>McDonald, Damen</t>
+        </is>
+      </c>
+      <c r="G46" s="88" t="n">
+        <v>44252</v>
+      </c>
+      <c r="H46" s="88" t="n">
+        <v>46230</v>
+      </c>
+      <c r="I46" s="88" t="n">
+        <v>46446</v>
+      </c>
+      <c r="J46" s="89" t="n">
+        <v>1205</v>
+      </c>
+      <c r="K46" s="89" t="n">
+        <v>1188</v>
+      </c>
+      <c r="L46" s="89" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2440 Eagles Eyrie-4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D47" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>White, Tateka</t>
+        </is>
+      </c>
+      <c r="G47" s="88" t="n">
+        <v>42777</v>
+      </c>
+      <c r="H47" s="88" t="n">
+        <v>46181</v>
+      </c>
+      <c r="I47" s="88" t="n">
+        <v>46551</v>
+      </c>
+      <c r="J47" s="89" t="n">
+        <v>1205</v>
+      </c>
+      <c r="K47" s="89" t="n">
+        <v>1151</v>
+      </c>
+      <c r="L47" s="89" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2440 Eagles Eyrie-5</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D48" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Harper, Kenyetta</t>
+        </is>
+      </c>
+      <c r="G48" s="88" t="n">
+        <v>45608</v>
+      </c>
+      <c r="H48" s="88" t="n">
+        <v>45971</v>
+      </c>
+      <c r="I48" s="88" t="n">
+        <v>46516</v>
+      </c>
+      <c r="J48" s="89" t="n">
+        <v>1280</v>
+      </c>
+      <c r="K48" s="89" t="n">
+        <v>1215</v>
+      </c>
+      <c r="L48" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2440 Eagles Eyrie-6</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="D49" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Catron, Michael</t>
+        </is>
+      </c>
+      <c r="G49" s="88" t="n">
+        <v>45891</v>
+      </c>
+      <c r="H49" s="88" t="n">
+        <v>46258</v>
+      </c>
+      <c r="I49" s="88" t="n">
+        <v>46628</v>
+      </c>
+      <c r="J49" s="89" t="n">
+        <v>1280</v>
+      </c>
+      <c r="K49" s="89" t="n">
+        <v>1263</v>
+      </c>
+      <c r="L49" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2441 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D50" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Dyke, Samuel</t>
+        </is>
+      </c>
+      <c r="G50" s="88" t="n">
+        <v>46151</v>
+      </c>
+      <c r="H50" s="88" t="n">
+        <v>46151</v>
+      </c>
+      <c r="I50" s="88" t="n">
+        <v>46516</v>
+      </c>
+      <c r="J50" s="89" t="n">
+        <v>1394</v>
+      </c>
+      <c r="K50" s="89" t="n">
+        <v>1285</v>
+      </c>
+      <c r="L50" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2441 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D51" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Price, Latosha</t>
+        </is>
+      </c>
+      <c r="G51" s="88" t="n">
+        <v>45380</v>
+      </c>
+      <c r="H51" s="88" t="n">
+        <v>46118</v>
+      </c>
+      <c r="I51" s="88" t="n">
+        <v>46488</v>
+      </c>
+      <c r="J51" s="89" t="n">
+        <v>1319</v>
+      </c>
+      <c r="K51" s="89" t="n">
+        <v>1328</v>
+      </c>
+      <c r="L51" s="89" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2443 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D52" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Washington, Samantha</t>
+        </is>
+      </c>
+      <c r="G52" s="88" t="n">
+        <v>45293</v>
+      </c>
+      <c r="H52" s="88" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I52" s="88" t="n">
+        <v>46544</v>
+      </c>
+      <c r="J52" s="89" t="n">
+        <v>1584</v>
+      </c>
+      <c r="K52" s="89" t="n">
+        <v>1386</v>
+      </c>
+      <c r="L52" s="89" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2443 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D53" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Satterwhite, Joshua</t>
+        </is>
+      </c>
+      <c r="G53" s="88" t="n">
+        <v>45778</v>
+      </c>
+      <c r="H53" s="88" t="n">
+        <v>46181</v>
+      </c>
+      <c r="I53" s="88" t="n">
+        <v>46551</v>
+      </c>
+      <c r="J53" s="89" t="n">
+        <v>1659</v>
+      </c>
+      <c r="K53" s="89" t="n">
+        <v>1769</v>
+      </c>
+      <c r="L53" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2445 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D54" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vinson, Clarissa</t>
+        </is>
+      </c>
+      <c r="G54" s="88" t="n">
+        <v>46141</v>
+      </c>
+      <c r="H54" s="88" t="n">
+        <v>46140</v>
+      </c>
+      <c r="I54" s="88" t="n">
+        <v>46509</v>
+      </c>
+      <c r="J54" s="89" t="n">
+        <v>1394</v>
+      </c>
+      <c r="K54" s="89" t="n">
+        <v>1217</v>
+      </c>
+      <c r="L54" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2445 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D55" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Marshall, Macy</t>
+        </is>
+      </c>
+      <c r="G55" s="88" t="n">
+        <v>38596</v>
+      </c>
+      <c r="H55" s="88" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I55" s="88" t="n">
+        <v>46299</v>
+      </c>
+      <c r="J55" s="89" t="n">
+        <v>1319</v>
+      </c>
+      <c r="K55" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L55" s="89" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2447 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D56" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Mitchell, Vanda</t>
+        </is>
+      </c>
+      <c r="G56" s="88" t="n">
+        <v>45985</v>
+      </c>
+      <c r="H56" s="88" t="n">
+        <v>45985</v>
+      </c>
+      <c r="I56" s="88" t="n">
+        <v>46474</v>
+      </c>
+      <c r="J56" s="89" t="n">
+        <v>1709</v>
+      </c>
+      <c r="K56" s="89" t="n">
+        <v>1600</v>
+      </c>
+      <c r="L56" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2447 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D57" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Vacant Unrented Not Ready</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="J57" s="89" t="n">
+        <v>1679</v>
+      </c>
+      <c r="K57" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2449 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D58" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Shellman, Termaine</t>
+        </is>
+      </c>
+      <c r="G58" s="88" t="n">
+        <v>41713</v>
+      </c>
+      <c r="H58" s="88" t="n">
+        <v>45931</v>
+      </c>
+      <c r="I58" s="88" t="n">
+        <v>46299</v>
+      </c>
+      <c r="J58" s="89" t="n">
+        <v>1319</v>
+      </c>
+      <c r="K58" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L58" s="89" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2449 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D59" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Lillie, Amelia</t>
+        </is>
+      </c>
+      <c r="G59" s="88" t="n">
+        <v>45427</v>
+      </c>
+      <c r="H59" s="88" t="n">
+        <v>46174</v>
+      </c>
+      <c r="I59" s="88" t="n">
+        <v>46390</v>
+      </c>
+      <c r="J59" s="89" t="n">
+        <v>1319</v>
+      </c>
+      <c r="K59" s="89" t="n">
+        <v>1360</v>
+      </c>
+      <c r="L59" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2451 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D60" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Holliger, Ethen</t>
+        </is>
+      </c>
+      <c r="G60" s="88" t="n">
+        <v>46189</v>
+      </c>
+      <c r="H60" s="88" t="n">
+        <v>46189</v>
+      </c>
+      <c r="I60" s="88" t="n">
+        <v>46558</v>
+      </c>
+      <c r="J60" s="89" t="n">
+        <v>1659</v>
+      </c>
+      <c r="K60" s="89" t="n">
+        <v>1572</v>
+      </c>
+      <c r="L60" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2451 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D61" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Caplinger, Holden</t>
+        </is>
+      </c>
+      <c r="G61" s="88" t="n">
+        <v>45821</v>
+      </c>
+      <c r="H61" s="88" t="n">
+        <v>46188</v>
+      </c>
+      <c r="I61" s="88" t="n">
+        <v>46558</v>
+      </c>
+      <c r="J61" s="89" t="n">
+        <v>1584</v>
+      </c>
+      <c r="K61" s="89" t="n">
+        <v>1734</v>
+      </c>
+      <c r="L61" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2453 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D62" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mitchell, LaTesha</t>
+        </is>
+      </c>
+      <c r="G62" s="88" t="n">
+        <v>46256</v>
+      </c>
+      <c r="H62" s="88" t="n">
+        <v>46256</v>
+      </c>
+      <c r="I62" s="88" t="n">
+        <v>46621</v>
+      </c>
+      <c r="J62" s="89" t="n">
+        <v>1719</v>
+      </c>
+      <c r="K62" s="89" t="n">
+        <v>1682</v>
+      </c>
+      <c r="L62" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2453 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D63" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Bucklew, Keith</t>
+        </is>
+      </c>
+      <c r="G63" s="88" t="n">
+        <v>44224</v>
+      </c>
+      <c r="H63" s="88" t="n">
+        <v>46146</v>
+      </c>
+      <c r="I63" s="88" t="n">
+        <v>46516</v>
+      </c>
+      <c r="J63" s="89" t="n">
+        <v>1319</v>
+      </c>
+      <c r="K63" s="89" t="n">
+        <v>1168</v>
+      </c>
+      <c r="L63" s="89" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2455 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D64" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Vacant Unrented Ready</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="J64" s="89" t="n">
+        <v>2099</v>
+      </c>
+      <c r="K64" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2455 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D65" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Sanz, Douglas</t>
+        </is>
+      </c>
+      <c r="G65" s="88" t="n">
+        <v>46202</v>
+      </c>
+      <c r="H65" s="88" t="n">
+        <v>46202</v>
+      </c>
+      <c r="I65" s="88" t="n">
+        <v>46537</v>
+      </c>
+      <c r="J65" s="89" t="n">
+        <v>1659</v>
+      </c>
+      <c r="K65" s="89" t="n">
+        <v>1576</v>
+      </c>
+      <c r="L65" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2457 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D66" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Anthony, Hunter</t>
+        </is>
+      </c>
+      <c r="G66" s="88" t="n">
+        <v>46143</v>
+      </c>
+      <c r="H66" s="88" t="n">
+        <v>46143</v>
+      </c>
+      <c r="I66" s="88" t="n">
+        <v>46509</v>
+      </c>
+      <c r="J66" s="89" t="n">
+        <v>1394</v>
+      </c>
+      <c r="K66" s="89" t="n">
+        <v>1299</v>
+      </c>
+      <c r="L66" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2457 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D67" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Gutgsell, Ashley</t>
+        </is>
+      </c>
+      <c r="G67" s="88" t="n">
+        <v>45404</v>
+      </c>
+      <c r="H67" s="88" t="n">
+        <v>46146</v>
+      </c>
+      <c r="I67" s="88" t="n">
+        <v>46516</v>
+      </c>
+      <c r="J67" s="89" t="n">
+        <v>1319</v>
+      </c>
+      <c r="K67" s="89" t="n">
+        <v>1315</v>
+      </c>
+      <c r="L67" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2459 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D68" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Sullivan, Nicholas</t>
+        </is>
+      </c>
+      <c r="G68" s="88" t="n">
+        <v>45975</v>
+      </c>
+      <c r="H68" s="88" t="n">
+        <v>45975</v>
+      </c>
+      <c r="I68" s="88" t="n">
+        <v>46404</v>
+      </c>
+      <c r="J68" s="89" t="n">
+        <v>1659</v>
+      </c>
+      <c r="K68" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L68" s="89" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2459 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D69" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mueller, Jake</t>
+        </is>
+      </c>
+      <c r="G69" s="88" t="n">
+        <v>45443</v>
+      </c>
+      <c r="H69" s="88" t="n">
+        <v>46175</v>
+      </c>
+      <c r="I69" s="88" t="n">
+        <v>46544</v>
+      </c>
+      <c r="J69" s="89" t="n">
+        <v>1584</v>
+      </c>
+      <c r="K69" s="89" t="n">
+        <v>1494</v>
+      </c>
+      <c r="L69" s="89" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2461 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D70" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Vacant Unrented Ready</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="J70" s="89" t="n">
+        <v>1349</v>
+      </c>
+      <c r="K70" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2461 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D71" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Vacant Rented Not Ready</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="J71" s="89" t="n">
+        <v>1394</v>
+      </c>
+      <c r="K71" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2463 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D72" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Holloway, Kyle</t>
+        </is>
+      </c>
+      <c r="G72" s="88" t="n">
+        <v>45488</v>
+      </c>
+      <c r="H72" s="88" t="n">
+        <v>46209</v>
+      </c>
+      <c r="I72" s="88" t="n">
+        <v>46579</v>
+      </c>
+      <c r="J72" s="89" t="n">
+        <v>1584</v>
+      </c>
+      <c r="K72" s="89" t="n">
+        <v>1535</v>
+      </c>
+      <c r="L72" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2463 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D73" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Krystofiak, Caden</t>
+        </is>
+      </c>
+      <c r="G73" s="88" t="n">
+        <v>45810</v>
+      </c>
+      <c r="H73" s="88" t="n">
+        <v>46181</v>
+      </c>
+      <c r="I73" s="88" t="n">
+        <v>46551</v>
+      </c>
+      <c r="J73" s="89" t="n">
+        <v>1659</v>
+      </c>
+      <c r="K73" s="89" t="n">
+        <v>1700</v>
+      </c>
+      <c r="L73" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2465 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D74" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Pugh, Jamie</t>
+        </is>
+      </c>
+      <c r="G74" s="88" t="n">
+        <v>46171</v>
+      </c>
+      <c r="H74" s="88" t="n">
+        <v>46171</v>
+      </c>
+      <c r="I74" s="88" t="n">
+        <v>46537</v>
+      </c>
+      <c r="J74" s="89" t="n">
+        <v>1394</v>
+      </c>
+      <c r="K74" s="89" t="n">
+        <v>1355</v>
+      </c>
+      <c r="L74" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2465 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D75" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Dunn, Makayla</t>
+        </is>
+      </c>
+      <c r="G75" s="88" t="n">
+        <v>45938</v>
+      </c>
+      <c r="H75" s="88" t="n">
+        <v>45938</v>
+      </c>
+      <c r="I75" s="88" t="n">
+        <v>46488</v>
+      </c>
+      <c r="J75" s="89" t="n">
+        <v>1394</v>
+      </c>
+      <c r="K75" s="89" t="n">
+        <v>1370</v>
+      </c>
+      <c r="L75" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2467 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D76" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Bickers, Jason</t>
+        </is>
+      </c>
+      <c r="G76" s="88" t="n">
+        <v>45418</v>
+      </c>
+      <c r="H76" s="88" t="n">
+        <v>46174</v>
+      </c>
+      <c r="I76" s="88" t="n">
+        <v>46544</v>
+      </c>
+      <c r="J76" s="89" t="n">
+        <v>1584</v>
+      </c>
+      <c r="K76" s="89" t="n">
+        <v>1494</v>
+      </c>
+      <c r="L76" s="89" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2467 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D77" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Frank, Sean</t>
+        </is>
+      </c>
+      <c r="G77" s="88" t="n">
+        <v>45408</v>
+      </c>
+      <c r="H77" s="88" t="n">
+        <v>46146</v>
+      </c>
+      <c r="I77" s="88" t="n">
+        <v>46362</v>
+      </c>
+      <c r="J77" s="89" t="n">
+        <v>1584</v>
+      </c>
+      <c r="K77" s="89" t="n">
+        <v>1494</v>
+      </c>
+      <c r="L77" s="89" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2469 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D78" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Lanier, Philip</t>
+        </is>
+      </c>
+      <c r="G78" s="88" t="n">
+        <v>43313</v>
+      </c>
+      <c r="H78" s="88" t="n">
+        <v>46209</v>
+      </c>
+      <c r="I78" s="88" t="n">
+        <v>46579</v>
+      </c>
+      <c r="J78" s="89" t="n">
+        <v>1319</v>
+      </c>
+      <c r="K78" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L78" s="89" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2469 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D79" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Caldwell, James</t>
+        </is>
+      </c>
+      <c r="G79" s="88" t="n">
+        <v>46188</v>
+      </c>
+      <c r="H79" s="88" t="n">
+        <v>46188</v>
+      </c>
+      <c r="I79" s="88" t="n">
+        <v>46558</v>
+      </c>
+      <c r="J79" s="89" t="n">
+        <v>1444</v>
+      </c>
+      <c r="K79" s="89" t="n">
+        <v>1575</v>
+      </c>
+      <c r="L79" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2471 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D80" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Johnson, Christopher</t>
+        </is>
+      </c>
+      <c r="G80" s="88" t="n">
+        <v>43503</v>
+      </c>
+      <c r="H80" s="88" t="n">
+        <v>46174</v>
+      </c>
+      <c r="I80" s="88" t="n">
+        <v>46390</v>
+      </c>
+      <c r="J80" s="89" t="n">
+        <v>1584</v>
+      </c>
+      <c r="K80" s="89" t="n">
+        <v>1555</v>
+      </c>
+      <c r="L80" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2471 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D81" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>DeVuono, Joseph</t>
+        </is>
+      </c>
+      <c r="G81" s="88" t="n">
+        <v>45380</v>
+      </c>
+      <c r="H81" s="88" t="n">
+        <v>46118</v>
+      </c>
+      <c r="I81" s="88" t="n">
+        <v>46488</v>
+      </c>
+      <c r="J81" s="89" t="n">
+        <v>1584</v>
+      </c>
+      <c r="K81" s="89" t="n">
+        <v>1361</v>
+      </c>
+      <c r="L81" s="89" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2473 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D82" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Vacant Rented Ready</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-- Vacant --</t>
+        </is>
+      </c>
+      <c r="J82" s="89" t="n">
+        <v>1394</v>
+      </c>
+      <c r="K82" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2473 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D83" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Notice Unrented</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Chamberlain, Damon</t>
+        </is>
+      </c>
+      <c r="G83" s="88" t="n">
+        <v>45576</v>
+      </c>
+      <c r="H83" s="88" t="n">
+        <v>45962</v>
+      </c>
+      <c r="I83" s="88" t="n">
+        <v>46299</v>
+      </c>
+      <c r="J83" s="89" t="n">
+        <v>1449</v>
+      </c>
+      <c r="K83" s="89" t="n">
+        <v>1332</v>
+      </c>
+      <c r="L83" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2475 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D84" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Pennington, Raejon</t>
+        </is>
+      </c>
+      <c r="G84" s="88" t="n">
+        <v>46025</v>
+      </c>
+      <c r="H84" s="88" t="n">
+        <v>46025</v>
+      </c>
+      <c r="I84" s="88" t="n">
+        <v>46572</v>
+      </c>
+      <c r="J84" s="89" t="n">
+        <v>1659</v>
+      </c>
+      <c r="K84" s="89" t="n">
+        <v>1564</v>
+      </c>
+      <c r="L84" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2475 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D85" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Saul, Ryan</t>
+        </is>
+      </c>
+      <c r="G85" s="88" t="n">
+        <v>45197</v>
+      </c>
+      <c r="H85" s="88" t="n">
+        <v>46023</v>
+      </c>
+      <c r="I85" s="88" t="n">
+        <v>46481</v>
+      </c>
+      <c r="J85" s="89" t="n">
+        <v>1584</v>
+      </c>
+      <c r="K85" s="89" t="n">
+        <v>1489</v>
+      </c>
+      <c r="L85" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2477 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="D86" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Suraba, Jake</t>
+        </is>
+      </c>
+      <c r="G86" s="88" t="n">
+        <v>45792</v>
+      </c>
+      <c r="H86" s="88" t="n">
+        <v>46160</v>
+      </c>
+      <c r="I86" s="88" t="n">
+        <v>46495</v>
+      </c>
+      <c r="J86" s="89" t="n">
+        <v>1444</v>
+      </c>
+      <c r="K86" s="89" t="n">
+        <v>1402</v>
+      </c>
+      <c r="L86" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>EAGL</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2479 N Peterson Ct-1</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="D87" s="87" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Gregory, Scott</t>
+        </is>
+      </c>
+      <c r="G87" s="88" t="n">
+        <v>41836</v>
+      </c>
+      <c r="H87" s="88" t="n">
+        <v>46054</v>
+      </c>
+      <c r="I87" s="88" t="n">
+        <v>46418</v>
+      </c>
+      <c r="J87" s="89" t="n">
+        <v>1584</v>
+      </c>
+      <c r="K87" s="89" t="n">
+        <v>1466</v>
+      </c>
+      <c r="L87" s="89" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Eagles Eyrie Total:</t>
+        </is>
+      </c>
+      <c r="D88" s="87" t="n">
+        <v>112400</v>
+      </c>
+      <c r="J88" s="89" t="n">
+        <v>114490</v>
+      </c>
+      <c r="K88" s="89" t="n">
+        <v>100522</v>
+      </c>
+      <c r="L88" s="89" t="n">
+        <v>41963.5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Status Summary</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Charge Code Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Unit Count</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Charge Code</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Charge Code Type</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Status Summary: Scheduled Rent</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Status Summary: Scheduled Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Occupied No Notice</t>
+        </is>
+      </c>
+      <c r="B92" s="87" t="n">
+        <v>71</v>
+      </c>
+      <c r="C92" s="90" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="D92" s="91" t="inlineStr">
+        <is>
+          <t>Ledger: Resident</t>
+        </is>
+      </c>
+      <c r="N92" s="89" t="n">
+        <v>96416</v>
+      </c>
+      <c r="O92" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Notice Unrented</t>
+        </is>
+      </c>
+      <c r="B93" s="87" t="n">
+        <v>3</v>
+      </c>
+      <c r="C93" s="90" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Amenity Rent</t>
+        </is>
+      </c>
+      <c r="E93" s="89" t="n">
+        <v>3350</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="N93" s="89" t="n">
+        <v>4106</v>
+      </c>
+      <c r="O93" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Total Occupied Units</t>
+        </is>
+      </c>
+      <c r="B94" s="92" t="n">
+        <v>74</v>
+      </c>
+      <c r="C94" s="90" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="E94" s="89" t="n">
+        <v>97172</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="N94" s="89" t="n">
+        <v>100522</v>
+      </c>
+      <c r="O94" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Vacant Rented Ready</t>
+        </is>
+      </c>
+      <c r="B95" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="C95" s="90" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Resident Total:</t>
+        </is>
+      </c>
+      <c r="E95" s="89" t="n">
+        <v>100522</v>
+      </c>
+      <c r="N95" s="89" t="n">
+        <v>1436</v>
+      </c>
+      <c r="O95" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Vacant Rented Not Ready</t>
+        </is>
+      </c>
+      <c r="B96" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" s="90" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Total:</t>
+        </is>
+      </c>
+      <c r="E96" s="89" t="n">
+        <v>100522</v>
+      </c>
+      <c r="N96" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Vacant Unrented Ready</t>
+        </is>
+      </c>
+      <c r="B97" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="C97" s="90" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="N97" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Vacant Unrented Not Ready</t>
+        </is>
+      </c>
+      <c r="B98" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" s="90" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N98" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Total Vacant Units</t>
+        </is>
+      </c>
+      <c r="B99" s="92" t="n">
+        <v>6</v>
+      </c>
+      <c r="C99" s="90" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="N99" s="89" t="n">
+        <v>1436</v>
+      </c>
+      <c r="O99" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Total Rentable Units</t>
+        </is>
+      </c>
+      <c r="B100" s="92" t="n">
+        <v>80</v>
+      </c>
+      <c r="C100" s="90" t="n">
+        <v>1</v>
+      </c>
+      <c r="N100" s="89" t="n">
+        <v>101958</v>
+      </c>
+      <c r="O100" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Unit Type</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Rentable Units</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Occupied Units</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Market Rent</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Scheduled Charges</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Units</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Excluded Units</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: 0</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Budgeted Rent</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Market Rent</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Total Effective Rent</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Total Effective Rent With Gift</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Total Actual Rent</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Lease Rent</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Recurring Concessions</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Onetime Concessions</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Gift Incentives</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Scheduled Charges</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Scheduled Rent Sum</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Scheduled Other Sum</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Actual Charges</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Rentable Units Avg</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Rentable Unit Sqft</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Occupied Unit Sqft</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Total Unit Sqft</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Excluded Unit Sqft</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Total Lease Term</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Total Contract Length Months</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Average Charges by Unit Type Summary: Total Occupied Length Months</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="B104" s="87" t="n">
+        <v>24</v>
+      </c>
+      <c r="C104" s="87" t="n">
+        <v>23</v>
+      </c>
+      <c r="N104" s="87" t="n">
+        <v>24</v>
+      </c>
+      <c r="O104" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="87" t="n">
+        <v>101161</v>
+      </c>
+      <c r="Q104" s="87" t="n">
+        <v>30045</v>
+      </c>
+      <c r="R104" s="87" t="n">
+        <v>29613</v>
+      </c>
+      <c r="S104" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z104" s="87" t="n">
+        <v>27759</v>
+      </c>
+      <c r="AA104" s="87" t="n">
+        <v>27759</v>
+      </c>
+      <c r="AB104" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC104" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD104" s="87" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE104" s="87" t="n">
+        <v>31200</v>
+      </c>
+      <c r="AF104" s="87" t="n">
+        <v>29900</v>
+      </c>
+      <c r="AG104" s="87" t="n">
+        <v>31200</v>
+      </c>
+      <c r="AH104" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI104" s="87" t="n">
+        <v>277</v>
+      </c>
+      <c r="AJ104" s="87" t="n">
+        <v>277</v>
+      </c>
+      <c r="AK104" s="87" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="B105" s="87" t="n">
+        <v>28</v>
+      </c>
+      <c r="C105" s="87" t="n">
+        <v>25</v>
+      </c>
+      <c r="N105" s="87" t="n">
+        <v>28</v>
+      </c>
+      <c r="O105" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="87" t="n">
+        <v>101161</v>
+      </c>
+      <c r="Q105" s="87" t="n">
+        <v>38642</v>
+      </c>
+      <c r="R105" s="87" t="n">
+        <v>38140</v>
+      </c>
+      <c r="S105" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z105" s="87" t="n">
+        <v>33371</v>
+      </c>
+      <c r="AA105" s="87" t="n">
+        <v>33371</v>
+      </c>
+      <c r="AB105" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC105" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD105" s="87" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE105" s="87" t="n">
+        <v>36400</v>
+      </c>
+      <c r="AF105" s="87" t="n">
+        <v>32500</v>
+      </c>
+      <c r="AG105" s="87" t="n">
+        <v>36400</v>
+      </c>
+      <c r="AH105" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI105" s="87" t="n">
+        <v>303</v>
+      </c>
+      <c r="AJ105" s="87" t="n">
+        <v>303</v>
+      </c>
+      <c r="AK105" s="87" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>3x3 Townhouse</t>
+        </is>
+      </c>
+      <c r="B106" s="87" t="n">
+        <v>28</v>
+      </c>
+      <c r="C106" s="87" t="n">
+        <v>26</v>
+      </c>
+      <c r="N106" s="87" t="n">
+        <v>28</v>
+      </c>
+      <c r="O106" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" s="87" t="n">
+        <v>101161</v>
+      </c>
+      <c r="Q106" s="87" t="n">
+        <v>45803</v>
+      </c>
+      <c r="R106" s="87" t="n">
+        <v>46408</v>
+      </c>
+      <c r="S106" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" s="87" t="n">
+        <v>39392</v>
+      </c>
+      <c r="AA106" s="87" t="n">
+        <v>39392</v>
+      </c>
+      <c r="AB106" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC106" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD106" s="87" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE106" s="87" t="n">
+        <v>44800</v>
+      </c>
+      <c r="AF106" s="87" t="n">
+        <v>41600</v>
+      </c>
+      <c r="AG106" s="87" t="n">
+        <v>44800</v>
+      </c>
+      <c r="AH106" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI106" s="87" t="n">
+        <v>320</v>
+      </c>
+      <c r="AJ106" s="87" t="n">
+        <v>320</v>
+      </c>
+      <c r="AK106" s="87" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Average:</t>
+        </is>
+      </c>
+      <c r="B107" s="92" t="n">
+        <v>80</v>
+      </c>
+      <c r="C107" s="92" t="n">
+        <v>74</v>
+      </c>
+      <c r="D107" s="89" t="n">
+        <v>1427.0125</v>
+      </c>
+      <c r="E107" s="89" t="n">
+        <v>1358.405405405405</v>
+      </c>
+      <c r="N107" s="92" t="n">
+        <v>80</v>
+      </c>
+      <c r="O107" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="87" t="n">
+        <v>114490</v>
+      </c>
+      <c r="R107" s="87" t="n">
+        <v>114161</v>
+      </c>
+      <c r="S107" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="87" t="n">
+        <v>100522</v>
+      </c>
+      <c r="AA107" s="87" t="n">
+        <v>100522</v>
+      </c>
+      <c r="AB107" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC107" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD107" s="87" t="n">
+        <v>80</v>
+      </c>
+      <c r="AE107" s="87" t="n">
+        <v>112400</v>
+      </c>
+      <c r="AF107" s="87" t="n">
+        <v>104000</v>
+      </c>
+      <c r="AG107" s="87" t="n">
+        <v>112400</v>
+      </c>
+      <c r="AH107" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI107" s="87" t="n">
+        <v>900</v>
+      </c>
+      <c r="AJ107" s="87" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK107" s="87" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Future Resident Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Bldg-Unit</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Unit Type</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SQFT</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Unit Status</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Resident</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Move-In</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Lease Start</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Lease End</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Market Rent (RI)</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Scheduled Charges</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Deposit Held</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2473 Idlewylde Ct-1</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2x2 Townhouse</t>
+        </is>
+      </c>
+      <c r="C111" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Vacant Rented Ready</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Thangsing, Khamthianmang</t>
+        </is>
+      </c>
+      <c r="F111" s="88" t="n">
+        <v>46283</v>
+      </c>
+      <c r="G111" s="88" t="n">
+        <v>46283</v>
+      </c>
+      <c r="H111" s="88" t="n">
+        <v>46495</v>
+      </c>
+      <c r="I111" s="89" t="n">
+        <v>1394</v>
+      </c>
+      <c r="J111" s="89" t="n">
+        <v>1436</v>
+      </c>
+      <c r="K111" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Eagles Eyrie Total:</t>
+        </is>
+      </c>
+      <c r="C112" s="87" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I112" s="89" t="n">
+        <v>1394</v>
+      </c>
+      <c r="J112" s="89" t="n">
+        <v>1436</v>
+      </c>
+      <c r="K112" s="89" t="n">
+        <v>500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>